--- a/bench/corpus/clean-00.xlsx
+++ b/bench/corpus/clean-00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyank\Desktop\後藤さんのclaude\ai-builders-2026\gridlint\bench\corpus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45FB9CE9-E80C-411D-82BB-9CC04AB2B43A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16F56ED1-3060-430A-A0D3-B55BEAB436D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B699044F-17DF-4957-BC88-C254568783F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{64BBC94B-FA1D-4FFC-A3A4-A8B6D340B2B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="2" r:id="rId1"/>
@@ -564,7 +564,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C174983A-4744-4D98-B932-E0E31B1640C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44008274-4E03-4606-9CE5-8CE35900FBF2}">
   <dimension ref="A1:N31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1759,7 +1759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{182623CC-6335-4EE1-AB14-16B9BC8123D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E339708-C2B2-4998-AB40-331DCD24C0AD}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
